--- a/mapa_proyecto.xlsx
+++ b/mapa_proyecto.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Documents\detector_vida_acustico\detector_vida_acustico\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189AB2C0-64A1-4A61-A0C5-E5934723E102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,28 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>AUDIO DE ZONA 0 - AD21P (001)</t>
+  </si>
+  <si>
+    <t>AUDIOS SINTETICOS DiT (003)</t>
+  </si>
+  <si>
+    <t>AUDIOS VARIOS REALES (002)</t>
+  </si>
+  <si>
+    <t>FILTRO, ATENUADOR Y SIMULADOR DE SENAL DE AUDIO</t>
+  </si>
+  <si>
+    <t>MODELO DiT Latente + Convoluciones</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -49,8 +75,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -66,6 +101,117 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1030497</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>3362</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1040022</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>41462</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Conector recto de flecha 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC3FBAB0-E704-0ADE-1FDE-DC131DFFB440}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2252325" y="574862"/>
+          <a:ext cx="9525" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1092188</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1103586</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>164224</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Conector recto de flecha 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C32DF8E-C2CF-4175-A859-EF7B1288D1F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4389809" y="571500"/>
+          <a:ext cx="11398" cy="545224"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +476,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C3:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="3:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="C7" s="1"/>
+      <c r="D7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E4:E5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>